--- a/data/trans_orig/IQ2606_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42333</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36653</t>
+          <t>36354</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54595</t>
+          <t>53702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75250</t>
+          <t>74444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24013</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>25417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19938</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>47989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64595</t>
+          <t>64525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85692</t>
+          <t>86403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>37436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42787</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>61977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40340</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16399</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38075</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54139</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74821</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50065</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20532</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>36510</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16399</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31705</t>
+          <t>31986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75174</t>
+          <t>73526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98086</t>
+          <t>96477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78391</t>
+          <t>76494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102246</t>
+          <t>100728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158708</t>
+          <t>158270</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>193182</t>
+          <t>192195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57657</t>
+          <t>58684</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83144</t>
+          <t>82720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59070</t>
+          <t>57623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82461</t>
+          <t>82732</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>36762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36187</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56836</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62030</t>
+          <t>61813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87159</t>
+          <t>87708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43367</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62528</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39366</t>
+          <t>39368</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>57270</t>
+          <t>58874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87959</t>
+          <t>86679</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114042</t>
+          <t>113728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64669</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32745</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>35117</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>57080</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41357</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>42943</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>79808</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>29274</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>246413</t>
+          <t>246296</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>288961</t>
+          <t>287507</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>239367</t>
+          <t>238748</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>279802</t>
+          <t>280997</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>497618</t>
+          <t>497127</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>554460</t>
+          <t>553861</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>124100</t>
+          <t>123051</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>159136</t>
+          <t>159451</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>114410</t>
+          <t>114815</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>147538</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>248117</t>
+          <t>247133</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>294510</t>
+          <t>295070</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>101694</t>
+          <t>100052</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>135028</t>
+          <t>133612</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>100651</t>
+          <t>100202</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>133121</t>
+          <t>132365</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>208758</t>
+          <t>210084</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>256038</t>
+          <t>258726</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>46739</t>
+          <t>47140</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>70394</t>
+          <t>70984</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>84118</t>
+          <t>84107</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>114774</t>
+          <t>114739</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>79498</t>
+          <t>79334</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>108362</t>
+          <t>112218</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>106668</t>
+          <t>105811</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>140448</t>
+          <t>140699</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>196527</t>
+          <t>194758</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>239325</t>
+          <t>240539</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36696</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51010</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>45484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61495</t>
+          <t>61073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86531</t>
+          <t>87110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107689</t>
+          <t>109272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>35761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42547</t>
+          <t>41998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63444</t>
+          <t>62701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57398</t>
+          <t>57083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45354</t>
+          <t>44815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>62847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114586</t>
+          <t>115215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>40306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39947</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52091</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74347</t>
+          <t>73982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>21458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>43611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62181</t>
+          <t>62134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32067</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>49426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27298</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>24003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>91474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115770</t>
+          <t>115599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69988</t>
+          <t>70249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92766</t>
+          <t>93680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>168113</t>
+          <t>168402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202850</t>
+          <t>202974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46907</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>67735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55408</t>
+          <t>54483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77145</t>
+          <t>77411</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105902</t>
+          <t>107201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138039</t>
+          <t>137622</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37535</t>
+          <t>37153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38514</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46858</t>
+          <t>47195</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70275</t>
+          <t>69351</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>30562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>31174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>56589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>44451</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62653</t>
+          <t>62915</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48714</t>
+          <t>48385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68378</t>
+          <t>68437</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>98692</t>
+          <t>98863</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>125794</t>
+          <t>125383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49673</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>61384</t>
+          <t>62993</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85879</t>
+          <t>86068</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>28639</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47268</t>
+          <t>47947</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>19658</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,49 +8935,49 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>20990</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>14404</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>29386</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>14,77%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>20,68%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>20990</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>14106</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>28941</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22843</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>42838</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>60983</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48488</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>277526</t>
+          <t>276443</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>318109</t>
+          <t>315675</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>283485</t>
+          <t>283770</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>328511</t>
+          <t>325735</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>572382</t>
+          <t>572964</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>633091</t>
+          <t>629738</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>165018</t>
+          <t>164594</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>201694</t>
+          <t>202918</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>187693</t>
+          <t>188284</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>228279</t>
+          <t>226766</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>366816</t>
+          <t>364932</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>420276</t>
+          <t>420141</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>72567</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>101036</t>
+          <t>100626</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>72336</t>
+          <t>73719</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>100028</t>
+          <t>101364</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>152062</t>
+          <t>152219</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>190266</t>
+          <t>193591</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>29364</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>24368</t>
+          <t>24165</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>43911</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>65459</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>61644</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>88575</t>
+          <t>88947</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>58474</t>
+          <t>57851</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>85266</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>127398</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>165702</t>
+          <t>165510</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33336</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16706</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19006</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,23%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19676</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>829</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>853</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48298</t>
+          <t>47403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48356</t>
+          <t>48245</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25292</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>36720</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32793</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>24614</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>47899</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>68265</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>59541</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>83865</t>
+          <t>84747</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>114669</t>
+          <t>115108</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>145634</t>
+          <t>145987</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>49490</t>
+          <t>48693</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>69624</t>
+          <t>69018</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>79795</t>
+          <t>78817</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>105086</t>
+          <t>105247</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>134748</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>167888</t>
+          <t>167912</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26934</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,47 +15116,47 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>36395</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>27426</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>46879</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t>14,27%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>36395</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>27735</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>47111</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
